--- a/French Ligue 1/X_pred.xlsx
+++ b/French Ligue 1/X_pred.xlsx
@@ -1553,16 +1553,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1577,88 +1577,88 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
@@ -1676,22 +1676,22 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
         <v>1</v>
@@ -1700,22 +1700,22 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1739,100 +1739,100 @@
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.233532934131737</v>
+        <v>3.368263473053892</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.741317365269461</v>
+        <v>3.911377245508982</v>
       </c>
       <c r="BO2" t="n">
-        <v>35.88323353293413</v>
+        <v>34.2245508982036</v>
       </c>
       <c r="BP2" t="n">
-        <v>11.00419161676647</v>
+        <v>11.73413173652695</v>
       </c>
       <c r="BQ2" t="n">
-        <v>138.2700598802395</v>
+        <v>128.5865269461078</v>
       </c>
       <c r="BR2" t="n">
-        <v>24.40059880239521</v>
+        <v>35.20239520958084</v>
       </c>
       <c r="BS2" t="n">
-        <v>16.74550898203593</v>
+        <v>16.13443113772455</v>
       </c>
       <c r="BT2" t="n">
-        <v>41.62455089820359</v>
+        <v>47.42544910179641</v>
       </c>
       <c r="BU2" t="n">
-        <v>1589.866467065868</v>
+        <v>1478.500598802395</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.57724550898204</v>
+        <v>35.20239520958084</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.43952095808383</v>
+        <v>16.62335329341317</v>
       </c>
       <c r="BX2" t="n">
-        <v>24.40059880239521</v>
+        <v>21.5125748502994</v>
       </c>
       <c r="BY2" t="n">
-        <v>46.8874251497006</v>
+        <v>55.24820359281438</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.870658682634731</v>
+        <v>1.955688622754491</v>
       </c>
       <c r="CA2" t="n">
-        <v>17.70239520958084</v>
+        <v>16.13443113772455</v>
       </c>
       <c r="CB2" t="n">
-        <v>43.05988023952096</v>
+        <v>36.18023952095809</v>
       </c>
       <c r="CC2" t="n">
-        <v>125.3520958083832</v>
+        <v>121.7416167664671</v>
       </c>
       <c r="CD2" t="n">
-        <v>1357.343113772455</v>
+        <v>1231.105988023952</v>
       </c>
       <c r="CE2" t="n">
-        <v>1177.926946107784</v>
+        <v>1046.782335329341</v>
       </c>
       <c r="CF2" t="n">
-        <v>205.012874251497</v>
+        <v>206.5696107784431</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.4586288030000606</v>
+        <v>0.2944454854859047</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.9141163128288878</v>
+        <v>0.9489439594005463</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.3402262142381903</v>
+        <v>0.06377245508982037</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.8744876912840986</v>
+        <v>0.5909712974982435</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.07405747476440996</v>
+        <v>0.09607416076458339</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.2443112523130875</v>
+        <v>0.2489430416455954</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.05012874251497</v>
+        <v>2.065696107784431</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.357999734796142</v>
+        <v>1.458386476738009</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1141306187692767</v>
+        <v>0.1127079572995528</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.381827471687566</v>
+        <v>1.28620737490187</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.353763092025709</v>
+        <v>1.278605621920391</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1035187556196057</v>
+        <v>0.1294058776303634</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         <v>1</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>1</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="DH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ2" t="n">
         <v>1</v>
@@ -1892,10 +1892,10 @@
         <v>1</v>
       </c>
       <c r="DL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
@@ -1907,34 +1907,34 @@
         <v>1</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX2" t="n">
         <v>1</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA2" t="n">
         <v>0</v>
@@ -1946,46 +1946,46 @@
         <v>1</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
         <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK2" t="n">
         <v>1</v>
       </c>
       <c r="EL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
         <v>1</v>
       </c>
       <c r="EP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
@@ -2003,228 +2003,228 @@
         <v>1</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA2" t="n">
         <v>1</v>
       </c>
       <c r="FB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>2.103293413173652</v>
+        <v>1.736526946107784</v>
       </c>
       <c r="FF2" t="n">
-        <v>6.442739520958084</v>
+        <v>1.729940119760479</v>
       </c>
       <c r="FG2" t="n">
-        <v>49.78480538922156</v>
+        <v>24.79580838323353</v>
       </c>
       <c r="FH2" t="n">
-        <v>13.47118263473054</v>
+        <v>8.649700598802395</v>
       </c>
       <c r="FI2" t="n">
-        <v>138.811751497006</v>
+        <v>100.3365269461078</v>
       </c>
       <c r="FJ2" t="n">
-        <v>41.58495508982036</v>
+        <v>29.98562874251497</v>
       </c>
       <c r="FK2" t="n">
-        <v>14.05688622754491</v>
+        <v>8.649700598802395</v>
       </c>
       <c r="FL2" t="n">
-        <v>66.18450598802396</v>
+        <v>34.59880239520958</v>
       </c>
       <c r="FM2" t="n">
-        <v>1655.198353293413</v>
+        <v>1379.338922155689</v>
       </c>
       <c r="FN2" t="n">
-        <v>42.17065868263473</v>
+        <v>60.54790419161677</v>
       </c>
       <c r="FO2" t="n">
-        <v>35.72791916167665</v>
+        <v>19.02934131736527</v>
       </c>
       <c r="FP2" t="n">
-        <v>32.79940119760479</v>
+        <v>20.18263473053892</v>
       </c>
       <c r="FQ2" t="n">
-        <v>58.57035928143713</v>
+        <v>83.61377245508982</v>
       </c>
       <c r="FR2" t="n">
-        <v>7.028443113772455</v>
+        <v>4.613173652694611</v>
       </c>
       <c r="FS2" t="n">
-        <v>18.15681137724551</v>
+        <v>27.10239520958084</v>
       </c>
       <c r="FT2" t="n">
-        <v>53.88473053892216</v>
+        <v>34.02215568862275</v>
       </c>
       <c r="FU2" t="n">
-        <v>164.5827095808383</v>
+        <v>147.0449101796407</v>
       </c>
       <c r="FV2" t="n">
-        <v>1319.004491017964</v>
+        <v>1044.883832335329</v>
       </c>
       <c r="FW2" t="n">
-        <v>1057.780688622754</v>
+        <v>844.7874251497005</v>
       </c>
       <c r="FX2" t="n">
-        <v>234.222866766467</v>
+        <v>229.1017365269461</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.359936573229745</v>
+        <v>0.1938173652694611</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.734214211517669</v>
+        <v>0.8731022570244127</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.4490394211576846</v>
+        <v>0.1970209580838323</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.168153276779774</v>
+        <v>0.9966942585417401</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.1484693164019818</v>
+        <v>0.09155611113107451</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3719965903828787</v>
+        <v>0.4375098000475938</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.342228667664671</v>
+        <v>2.291017365269461</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.300657297429994</v>
+        <v>1.397057702776266</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1537357126215362</v>
+        <v>0.1116162261312302</v>
       </c>
       <c r="GH2" t="n">
-        <v>1.380592007894208</v>
+        <v>1.001725041493706</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.399581963105085</v>
+        <v>1.099053780335115</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.1802753371357581</v>
+        <v>0.1137860189333649</v>
       </c>
       <c r="GK2" t="n">
-        <v>-0.7014221556886229</v>
+        <v>2.181437125748503</v>
       </c>
       <c r="GL2" t="n">
-        <v>-13.90157185628743</v>
+        <v>9.428742514970065</v>
       </c>
       <c r="GM2" t="n">
-        <v>-2.466991017964071</v>
+        <v>3.08443113772455</v>
       </c>
       <c r="GN2" t="n">
-        <v>-0.5416916167664567</v>
+        <v>28.25000000000003</v>
       </c>
       <c r="GO2" t="n">
-        <v>-17.18435628742515</v>
+        <v>5.216766467065874</v>
       </c>
       <c r="GP2" t="n">
-        <v>2.68862275449102</v>
+        <v>7.484730538922156</v>
       </c>
       <c r="GQ2" t="n">
-        <v>-24.55995508982036</v>
+        <v>12.82664670658683</v>
       </c>
       <c r="GR2" t="n">
-        <v>-65.33188622754506</v>
+        <v>99.16167664670661</v>
       </c>
       <c r="GS2" t="n">
-        <v>-10.59341317365269</v>
+        <v>-25.34550898203592</v>
       </c>
       <c r="GT2" t="n">
-        <v>-23.28839820359281</v>
+        <v>-2.405988023952094</v>
       </c>
       <c r="GU2" t="n">
-        <v>-8.398802395209575</v>
+        <v>1.329940119760483</v>
       </c>
       <c r="GV2" t="n">
-        <v>-11.68293413173652</v>
+        <v>-28.36556886227544</v>
       </c>
       <c r="GW2" t="n">
-        <v>-4.157784431137724</v>
+        <v>-2.65748502994012</v>
       </c>
       <c r="GX2" t="n">
-        <v>-0.4544161676646681</v>
+        <v>-10.96796407185629</v>
       </c>
       <c r="GY2" t="n">
-        <v>-10.82485029940119</v>
+        <v>2.158083832335336</v>
       </c>
       <c r="GZ2" t="n">
-        <v>-39.23061377245509</v>
+        <v>-25.30329341317365</v>
       </c>
       <c r="HA2" t="n">
-        <v>38.3386227544911</v>
+        <v>186.2221556886229</v>
       </c>
       <c r="HB2" t="n">
-        <v>120.14625748503</v>
+        <v>201.9949101796408</v>
       </c>
       <c r="HC2" t="n">
-        <v>-29.20999251497</v>
+        <v>-22.53212574850295</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.09869222977031561</v>
+        <v>0.1006281202164436</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.1799021013112189</v>
+        <v>0.07584170237613364</v>
       </c>
       <c r="HF2" t="n">
-        <v>-0.1088132069194944</v>
+        <v>-0.133248502994012</v>
       </c>
       <c r="HG2" t="n">
-        <v>-0.2936655854956751</v>
+        <v>-0.4057229610434966</v>
       </c>
       <c r="HH2" t="n">
-        <v>-0.07441184163757181</v>
+        <v>0.00451804963350888</v>
       </c>
       <c r="HI2" t="n">
-        <v>-0.1276853380697913</v>
+        <v>-0.1885667584019984</v>
       </c>
       <c r="HJ2" t="n">
-        <v>-0.2920999251497007</v>
+        <v>-0.2253212574850298</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.05734243736614841</v>
+        <v>0.06132877396174341</v>
       </c>
       <c r="HL2" t="n">
-        <v>-0.03960509385225949</v>
+        <v>0.001091731168322563</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.001235463793358038</v>
+        <v>0.2844823334081636</v>
       </c>
       <c r="HN2" t="n">
-        <v>-0.04581887107937677</v>
+        <v>0.1795518415852757</v>
       </c>
       <c r="HO2" t="n">
-        <v>-0.07675658151615239</v>
+        <v>0.0156198586969985</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -2236,34 +2236,34 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2275,10 +2275,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
@@ -2287,37 +2287,37 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>1</v>
@@ -2329,37 +2329,37 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -2368,19 +2368,19 @@
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -2398,10 +2398,10 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
         <v>1</v>
@@ -2410,121 +2410,121 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.79940119760479</v>
+        <v>2.058383233532934</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.77245508982036</v>
+        <v>2.295808383233533</v>
       </c>
       <c r="BO3" t="n">
-        <v>31.97544910179641</v>
+        <v>28.12365269461078</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.9311377245509</v>
+        <v>6.887425149700599</v>
       </c>
       <c r="BQ3" t="n">
-        <v>125.0383233532934</v>
+        <v>119.3820359281437</v>
       </c>
       <c r="BR3" t="n">
-        <v>30.5437125748503</v>
+        <v>32.14131736526946</v>
       </c>
       <c r="BS3" t="n">
-        <v>13.84011976047904</v>
+        <v>12.62694610778443</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.77005988023953</v>
+        <v>35.01107784431137</v>
       </c>
       <c r="BU3" t="n">
-        <v>1417.896407185629</v>
+        <v>1485.961976047904</v>
       </c>
       <c r="BV3" t="n">
-        <v>31.97544910179641</v>
+        <v>51.65568862275449</v>
       </c>
       <c r="BW3" t="n">
-        <v>20.04431137724551</v>
+        <v>22.95808383233533</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.27065868263473</v>
+        <v>37.8808383233533</v>
       </c>
       <c r="BY3" t="n">
-        <v>49.63353293413174</v>
+        <v>78.6314371257485</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.295209580838324</v>
+        <v>1.72185628742515</v>
       </c>
       <c r="CA3" t="n">
-        <v>15.74910179640719</v>
+        <v>26.40179640718563</v>
       </c>
       <c r="CB3" t="n">
-        <v>46.77005988023953</v>
+        <v>42.47245508982036</v>
       </c>
       <c r="CC3" t="n">
-        <v>111.6754491017964</v>
+        <v>173.3335329341317</v>
       </c>
       <c r="CD3" t="n">
-        <v>1179.750898203593</v>
+        <v>1186.932934131737</v>
       </c>
       <c r="CE3" t="n">
-        <v>966.4221556886229</v>
+        <v>942.4293413173652</v>
       </c>
       <c r="CF3" t="n">
-        <v>195.241137724551</v>
+        <v>226.0223353293413</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3261010541941328</v>
+        <v>0.2447736879182811</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.8860431528668584</v>
+        <v>0.816046268806924</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.3022554890219561</v>
+        <v>0.1003577056413489</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.9703992015968064</v>
+        <v>0.6862491558236908</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.09298495615672719</v>
+        <v>0.08367681208167717</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.2276848916632456</v>
+        <v>0.4277378618070189</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.952411377245509</v>
+        <v>2.260223353293413</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.344042166293978</v>
+        <v>1.621260546274865</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1170818205072783</v>
+        <v>0.1286820173402629</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.255497954127508</v>
+        <v>1.194542193643241</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.23307921569306</v>
+        <v>1.233769149041883</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1209484215726969</v>
+        <v>0.1130601051405756</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX3" t="n">
         <v>1</v>
       </c>
       <c r="CY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2533,19 +2533,19 @@
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC3" t="n">
         <v>1</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
         <v>1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
@@ -2557,76 +2557,76 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
         <v>1</v>
       </c>
       <c r="DL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
         <v>0</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY3" t="n">
         <v>1</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB3" t="n">
         <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED3" t="n">
         <v>1</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF3" t="n">
         <v>1</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
@@ -2638,25 +2638,25 @@
         <v>0</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>1</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
         <v>1</v>
@@ -2689,210 +2689,210 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FE3" t="n">
-        <v>2.058383233532934</v>
+        <v>2.537425149700599</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.767964071856288</v>
+        <v>3.829041916167664</v>
       </c>
       <c r="FG3" t="n">
-        <v>23.25089820359282</v>
+        <v>34.46137724550898</v>
       </c>
       <c r="FH3" t="n">
-        <v>6.089520958083833</v>
+        <v>10.94011976047904</v>
       </c>
       <c r="FI3" t="n">
-        <v>114.0401197604791</v>
+        <v>124.7173652694611</v>
       </c>
       <c r="FJ3" t="n">
-        <v>32.10838323353293</v>
+        <v>30.63233532934131</v>
       </c>
       <c r="FK3" t="n">
-        <v>11.62544910179641</v>
+        <v>10.94011976047904</v>
       </c>
       <c r="FL3" t="n">
-        <v>33.21556886227545</v>
+        <v>33.91437125748503</v>
       </c>
       <c r="FM3" t="n">
-        <v>1466.467365269461</v>
+        <v>1582.488323353293</v>
       </c>
       <c r="FN3" t="n">
-        <v>54.25209580838325</v>
+        <v>35.00838323353293</v>
       </c>
       <c r="FO3" t="n">
-        <v>24.91167664670659</v>
+        <v>19.14520958083832</v>
       </c>
       <c r="FP3" t="n">
-        <v>37.09071856287426</v>
+        <v>20.23922155688622</v>
       </c>
       <c r="FQ3" t="n">
-        <v>76.39580838323354</v>
+        <v>62.35868263473053</v>
       </c>
       <c r="FR3" t="n">
-        <v>2.21437125748503</v>
+        <v>7.111077844311377</v>
       </c>
       <c r="FS3" t="n">
-        <v>23.80449101796407</v>
+        <v>20.78622754491018</v>
       </c>
       <c r="FT3" t="n">
-        <v>44.84101796407186</v>
+        <v>40.47844311377245</v>
       </c>
       <c r="FU3" t="n">
-        <v>166.0778443113772</v>
+        <v>140.0335329341317</v>
       </c>
       <c r="FV3" t="n">
-        <v>1173.616766467066</v>
+        <v>1322.113473053892</v>
       </c>
       <c r="FW3" t="n">
-        <v>940.0005988023953</v>
+        <v>1111.516167664671</v>
       </c>
       <c r="FX3" t="n">
-        <v>219.9977844311377</v>
+        <v>226.8980838323353</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.3151757409550647</v>
+        <v>0.2749563915646966</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.8266417445221602</v>
+        <v>0.897406925279875</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1291716566866268</v>
+        <v>0.3684002449646162</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.6133456895732347</v>
+        <v>1.236150653238977</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.07679678045857286</v>
+        <v>0.06565081323220874</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.4000067495911361</v>
+        <v>0.3079728091268345</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.199977844311377</v>
+        <v>2.268980838323353</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.546161973976345</v>
+        <v>1.39010062454277</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1309233304481996</v>
+        <v>0.1026135772974293</v>
       </c>
       <c r="GH3" t="n">
-        <v>1.139041363008212</v>
+        <v>1.251326656505454</v>
       </c>
       <c r="GI3" t="n">
-        <v>1.183009643071313</v>
+        <v>1.267757511153803</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.1031548884097919</v>
+        <v>0.08740773104881676</v>
       </c>
       <c r="GK3" t="n">
-        <v>2.004491017964072</v>
+        <v>-1.533233532934131</v>
       </c>
       <c r="GL3" t="n">
-        <v>8.724550898203592</v>
+        <v>-6.337724550898198</v>
       </c>
       <c r="GM3" t="n">
-        <v>5.841616766467068</v>
+        <v>-4.052694610778442</v>
       </c>
       <c r="GN3" t="n">
-        <v>10.99820359281436</v>
+        <v>-5.335329341317347</v>
       </c>
       <c r="GO3" t="n">
-        <v>-1.56467065868263</v>
+        <v>1.508982035928145</v>
       </c>
       <c r="GP3" t="n">
-        <v>2.214670658682634</v>
+        <v>1.686826347305391</v>
       </c>
       <c r="GQ3" t="n">
-        <v>13.55449101796408</v>
+        <v>1.096706586826343</v>
       </c>
       <c r="GR3" t="n">
-        <v>-48.57095808383224</v>
+        <v>-96.52634730538921</v>
       </c>
       <c r="GS3" t="n">
-        <v>-22.27664670658683</v>
+        <v>16.64730538922156</v>
       </c>
       <c r="GT3" t="n">
-        <v>-4.867365269461075</v>
+        <v>3.812874251497007</v>
       </c>
       <c r="GU3" t="n">
-        <v>-0.8200598802395263</v>
+        <v>17.64161676646707</v>
       </c>
       <c r="GV3" t="n">
-        <v>-26.7622754491018</v>
+        <v>16.27275449101797</v>
       </c>
       <c r="GW3" t="n">
-        <v>2.080838323353294</v>
+        <v>-5.389221556886227</v>
       </c>
       <c r="GX3" t="n">
-        <v>-8.055389221556885</v>
+        <v>5.615568862275452</v>
       </c>
       <c r="GY3" t="n">
-        <v>1.92904191616767</v>
+        <v>1.994011976047915</v>
       </c>
       <c r="GZ3" t="n">
-        <v>-54.40239520958083</v>
+        <v>33.30000000000001</v>
       </c>
       <c r="HA3" t="n">
-        <v>6.134131736527024</v>
+        <v>-135.1805389221554</v>
       </c>
       <c r="HB3" t="n">
-        <v>26.42155688622756</v>
+        <v>-169.0868263473053</v>
       </c>
       <c r="HC3" t="n">
-        <v>-24.75664670658676</v>
+        <v>-0.8757485029940142</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.01092531323906815</v>
+        <v>-0.03018270364641548</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.0594014083446982</v>
+        <v>-0.08136065647295099</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.1730838323353293</v>
+        <v>-0.2680425393232673</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3570535120235717</v>
+        <v>-0.5499014974152857</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.01618817569815434</v>
+        <v>0.01802599884946843</v>
       </c>
       <c r="HI3" t="n">
-        <v>-0.1723218579278906</v>
+        <v>0.1197650526801844</v>
       </c>
       <c r="HJ3" t="n">
-        <v>-0.2475664670658679</v>
+        <v>-0.008757485029939893</v>
       </c>
       <c r="HK3" t="n">
-        <v>-0.2021198076823671</v>
+        <v>0.2311599217320957</v>
       </c>
       <c r="HL3" t="n">
-        <v>-0.01384150994092137</v>
+        <v>0.02606844004283354</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.1164565911192952</v>
+        <v>-0.05678446286221339</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.05006957262174727</v>
+        <v>-0.03398836211191969</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.017793533162905</v>
+        <v>0.02565237409175888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -2901,25 +2901,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -2934,16 +2934,16 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2973,43 +2973,43 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -3045,25 +3045,25 @@
         <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
         <v>1</v>
@@ -3072,115 +3072,115 @@
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.008982035928144</v>
+        <v>2.604790419161677</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.032634730538922</v>
+        <v>2.733532934131736</v>
       </c>
       <c r="BO4" t="n">
-        <v>24.26107784431138</v>
+        <v>41.00299401197604</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.364970059880239</v>
+        <v>8.747305389221557</v>
       </c>
       <c r="BQ4" t="n">
-        <v>125.6377245508982</v>
+        <v>129.022754491018</v>
       </c>
       <c r="BR4" t="n">
-        <v>27.72694610778443</v>
+        <v>30.61556886227545</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.83083832335329</v>
+        <v>10.93413173652695</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.7565868263473</v>
+        <v>45.92335329341317</v>
       </c>
       <c r="BU4" t="n">
-        <v>1507.219461077844</v>
+        <v>1530.231736526946</v>
       </c>
       <c r="BV4" t="n">
-        <v>38.99101796407186</v>
+        <v>56.85748502994011</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.99700598802395</v>
+        <v>22.41497005988024</v>
       </c>
       <c r="BX4" t="n">
-        <v>23.39461077844312</v>
+        <v>48.65688622754491</v>
       </c>
       <c r="BY4" t="n">
-        <v>38.55778443113773</v>
+        <v>54.12395209580838</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.465868263473054</v>
+        <v>3.280239520958083</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.231437125748503</v>
+        <v>13.12095808383233</v>
       </c>
       <c r="CB4" t="n">
-        <v>38.12455089820359</v>
+        <v>54.67065868263472</v>
       </c>
       <c r="CC4" t="n">
-        <v>75.81586826347305</v>
+        <v>193.5341317365269</v>
       </c>
       <c r="CD4" t="n">
-        <v>1271.107185628742</v>
+        <v>1216.422155688623</v>
       </c>
       <c r="CE4" t="n">
-        <v>1101.279640718563</v>
+        <v>952.3628742514968</v>
       </c>
       <c r="CF4" t="n">
-        <v>187.1135628742515</v>
+        <v>211.5754491017964</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.3290824411782496</v>
+        <v>0.1767132401862941</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.7535637815278533</v>
+        <v>0.5454640718562873</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.444064371257485</v>
+        <v>0.7519605066887377</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.5764412840984696</v>
+        <v>1.340722258756899</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.07544124509000072</v>
+        <v>0.103383908759337</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1340692071760603</v>
+        <v>0.4538788995895917</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.871135628742515</v>
+        <v>2.115754491017964</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.121811483039028</v>
+        <v>1.357325982954726</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1277606273821223</v>
+        <v>0.1670024232440283</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.253010444332721</v>
+        <v>1.290538265716611</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.227466057340241</v>
+        <v>1.303760047082596</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.09443447200771826</v>
+        <v>0.1274407475079035</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU4" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX4" t="n">
         <v>1</v>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA4" t="n">
         <v>1</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3222,40 +3222,40 @@
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK4" t="n">
         <v>1</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP4" t="n">
         <v>1</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT4" t="n">
         <v>1</v>
@@ -3279,13 +3279,13 @@
         <v>1</v>
       </c>
       <c r="EA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
@@ -3294,16 +3294,16 @@
         <v>1</v>
       </c>
       <c r="EF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
         <v>0</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
         <v>1</v>
@@ -3321,31 +3321,31 @@
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP4" t="n">
         <v>1</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET4" t="n">
         <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA4" t="n">
         <v>1</v>
@@ -3369,193 +3369,193 @@
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>1.833832335329341</v>
+        <v>2.79940119760479</v>
       </c>
       <c r="FF4" t="n">
-        <v>5.510479041916168</v>
+        <v>5.038922155688623</v>
       </c>
       <c r="FG4" t="n">
-        <v>34.8997005988024</v>
+        <v>32.98203592814372</v>
       </c>
       <c r="FH4" t="n">
-        <v>14.69461077844311</v>
+        <v>12.36826347305389</v>
       </c>
       <c r="FI4" t="n">
-        <v>135.9251497005988</v>
+        <v>124.1407185628743</v>
       </c>
       <c r="FJ4" t="n">
-        <v>39.18562874251498</v>
+        <v>30.69161676646707</v>
       </c>
       <c r="FK4" t="n">
-        <v>9.796407185628745</v>
+        <v>14.20059880239521</v>
       </c>
       <c r="FL4" t="n">
-        <v>63.67664670658684</v>
+        <v>46.72455089820359</v>
       </c>
       <c r="FM4" t="n">
-        <v>1625.59131736527</v>
+        <v>1390.74251497006</v>
       </c>
       <c r="FN4" t="n">
-        <v>43.47155688622755</v>
+        <v>31.60778443113773</v>
       </c>
       <c r="FO4" t="n">
-        <v>23.26646706586826</v>
+        <v>17.86526946107784</v>
       </c>
       <c r="FP4" t="n">
-        <v>37.96107784431138</v>
+        <v>33.89820359281438</v>
       </c>
       <c r="FQ4" t="n">
-        <v>72.86077844311379</v>
+        <v>51.30538922155689</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.061377245508982</v>
+        <v>4.122754491017965</v>
       </c>
       <c r="FS4" t="n">
-        <v>25.10329341317365</v>
+        <v>16.94910179640719</v>
       </c>
       <c r="FT4" t="n">
-        <v>61.22754491017965</v>
+        <v>40.76946107784431</v>
       </c>
       <c r="FU4" t="n">
-        <v>211.8473053892216</v>
+        <v>111.314371257485</v>
       </c>
       <c r="FV4" t="n">
-        <v>1321.290419161677</v>
+        <v>1159.868263473054</v>
       </c>
       <c r="FW4" t="n">
-        <v>1031.684131736527</v>
+        <v>961.9760479041917</v>
       </c>
       <c r="FX4" t="n">
-        <v>235.9097305389221</v>
+        <v>189.7841317365269</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.5459456087824351</v>
+        <v>0.3371175881320067</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.29768379906853</v>
+        <v>0.847023780663081</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.7612563584120471</v>
+        <v>0.198502994011976</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.195945421843626</v>
+        <v>0.8463644140290846</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1477011584389101</v>
+        <v>0.09022205590165329</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.5158199945398355</v>
+        <v>0.2204928763420213</v>
       </c>
       <c r="GE4" t="n">
-        <v>2.359097305389222</v>
+        <v>1.89784131736527</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.481501855223722</v>
+        <v>1.204121880462677</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1276336847312931</v>
+        <v>0.1171550377007421</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.35819008309423</v>
+        <v>1.244519555887739</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.381134587901695</v>
+        <v>1.221289376250431</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.1705372057739149</v>
+        <v>0.1182239042100301</v>
       </c>
       <c r="GK4" t="n">
-        <v>-2.477844311377246</v>
+        <v>-2.305389221556887</v>
       </c>
       <c r="GL4" t="n">
-        <v>-10.63862275449102</v>
+        <v>8.020958083832326</v>
       </c>
       <c r="GM4" t="n">
-        <v>-7.329640718562874</v>
+        <v>-3.620958083832337</v>
       </c>
       <c r="GN4" t="n">
-        <v>-10.28742514970061</v>
+        <v>4.882035928143708</v>
       </c>
       <c r="GO4" t="n">
-        <v>-11.45868263473055</v>
+        <v>-0.076047904191622</v>
       </c>
       <c r="GP4" t="n">
-        <v>1.03443113772455</v>
+        <v>-3.266467065868264</v>
       </c>
       <c r="GQ4" t="n">
-        <v>-19.92005988023953</v>
+        <v>-0.801197604790417</v>
       </c>
       <c r="GR4" t="n">
-        <v>-118.3718562874253</v>
+        <v>139.4892215568857</v>
       </c>
       <c r="GS4" t="n">
-        <v>-4.480538922155688</v>
+        <v>25.24970059880239</v>
       </c>
       <c r="GT4" t="n">
-        <v>-10.26946107784431</v>
+        <v>4.549700598802392</v>
       </c>
       <c r="GU4" t="n">
-        <v>-14.56646706586827</v>
+        <v>14.75868263473053</v>
       </c>
       <c r="GV4" t="n">
-        <v>-34.30299401197606</v>
+        <v>2.818562874251491</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.4044910179640717</v>
+        <v>-0.8425149700598813</v>
       </c>
       <c r="GX4" t="n">
-        <v>-16.87185628742515</v>
+        <v>-3.828143712574855</v>
       </c>
       <c r="GY4" t="n">
-        <v>-23.10299401197605</v>
+        <v>13.90119760479041</v>
       </c>
       <c r="GZ4" t="n">
-        <v>-136.0314371257485</v>
+        <v>82.21976047904188</v>
       </c>
       <c r="HA4" t="n">
-        <v>-50.18323353293431</v>
+        <v>56.55389221556857</v>
       </c>
       <c r="HB4" t="n">
-        <v>69.59550898203588</v>
+        <v>-9.613173652694854</v>
       </c>
       <c r="HC4" t="n">
-        <v>-48.79616766467063</v>
+        <v>21.79131736526946</v>
       </c>
       <c r="HD4" t="n">
-        <v>-0.2168631676041856</v>
+        <v>-0.1604043479457126</v>
       </c>
       <c r="HE4" t="n">
-        <v>-0.5441200175406764</v>
+        <v>-0.3015597088067937</v>
       </c>
       <c r="HF4" t="n">
-        <v>-0.3171919871545621</v>
+        <v>0.5534575126767617</v>
       </c>
       <c r="HG4" t="n">
-        <v>-0.619504137745156</v>
+        <v>0.4943578447278146</v>
       </c>
       <c r="HH4" t="n">
-        <v>-0.07225991334890938</v>
+        <v>0.01316185285768368</v>
       </c>
       <c r="HI4" t="n">
-        <v>-0.3817507873637752</v>
+        <v>0.2333860232475704</v>
       </c>
       <c r="HJ4" t="n">
-        <v>-0.4879616766467072</v>
+        <v>0.2179131736526942</v>
       </c>
       <c r="HK4" t="n">
-        <v>-0.359690372184694</v>
+        <v>0.1532041024920485</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.0001269426508292704</v>
+        <v>0.04984738554328623</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.1051796387615089</v>
+        <v>0.04601870982887202</v>
       </c>
       <c r="HN4" t="n">
-        <v>-0.1536685305614538</v>
+        <v>0.08247067083216497</v>
       </c>
       <c r="HO4" t="n">
-        <v>-0.07610273376619667</v>
+        <v>0.009216843297873326</v>
       </c>
     </row>
     <row r="5">
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -3575,16 +3575,16 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -3602,16 +3602,16 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -3620,22 +3620,22 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3659,37 +3659,37 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
         <v>1</v>
@@ -3704,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -3719,19 +3719,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3743,118 +3743,118 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
         <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.290419161676647</v>
+        <v>2.889221556886227</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.24311377245509</v>
+        <v>5.825748502994013</v>
       </c>
       <c r="BO5" t="n">
-        <v>26.91736526946108</v>
+        <v>50.48982035928144</v>
       </c>
       <c r="BP5" t="n">
-        <v>11.21556886227545</v>
+        <v>14.88802395209581</v>
       </c>
       <c r="BQ5" t="n">
-        <v>135.1476047904192</v>
+        <v>157.2952095808383</v>
       </c>
       <c r="BR5" t="n">
-        <v>38.13293413173653</v>
+        <v>37.5437125748503</v>
       </c>
       <c r="BS5" t="n">
-        <v>14.58023952095808</v>
+        <v>22.65568862275449</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.98383233532933</v>
+        <v>70.5562874251497</v>
       </c>
       <c r="BU5" t="n">
-        <v>1585.881437125749</v>
+        <v>1938.032335329341</v>
       </c>
       <c r="BV5" t="n">
-        <v>48.22694610778443</v>
+        <v>57.61017964071857</v>
       </c>
       <c r="BW5" t="n">
-        <v>23.55269461077844</v>
+        <v>38.19101796407186</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.08592814371258</v>
+        <v>31.71796407185629</v>
       </c>
       <c r="BY5" t="n">
-        <v>67.2934131736527</v>
+        <v>64.73053892215569</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.925449101796407</v>
+        <v>4.531137724550898</v>
       </c>
       <c r="CA5" t="n">
-        <v>17.94491017964072</v>
+        <v>22.65568862275449</v>
       </c>
       <c r="CB5" t="n">
-        <v>47.66616766467066</v>
+        <v>42.72215568862276</v>
       </c>
       <c r="CC5" t="n">
-        <v>179.4491017964072</v>
+        <v>167.6520958083832</v>
       </c>
       <c r="CD5" t="n">
-        <v>1316.147005988024</v>
+        <v>1567.773652694611</v>
       </c>
       <c r="CE5" t="n">
-        <v>1068.282934131737</v>
+        <v>1286.843113772455</v>
       </c>
       <c r="CF5" t="n">
-        <v>225.2647005988024</v>
+        <v>265.9130538922155</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.2826145328390837</v>
+        <v>0.4984995526189002</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.1616124893071</v>
+        <v>0.9959619736493577</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.4095685414884517</v>
+        <v>0.2592023744718355</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.144819948016056</v>
+        <v>1.24510546007552</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.09613731934751371</v>
+        <v>0.1388888298351857</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.3934771611063066</v>
+        <v>0.3439395840669069</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.252647005988023</v>
+        <v>2.659130538922156</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.385570099118003</v>
+        <v>1.361737607942561</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1456149997397725</v>
+        <v>0.1853885767179429</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.354981526898431</v>
+        <v>1.568387472666081</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.350158008015619</v>
+        <v>1.580901769559569</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1261978415748529</v>
+        <v>0.1815003420897049</v>
       </c>
       <c r="CS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV5" t="n">
         <v>1</v>
@@ -3872,19 +3872,19 @@
         <v>1</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3893,43 +3893,43 @@
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
         <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ5" t="n">
         <v>1</v>
       </c>
       <c r="DR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU5" t="n">
         <v>1</v>
@@ -3938,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF5" t="n">
         <v>1</v>
@@ -3974,64 +3974,64 @@
         <v>1</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ5" t="n">
         <v>1</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>1</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
         <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC5" t="n">
         <v>1</v>
@@ -4040,1109 +4040,1109 @@
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>3.375748502994012</v>
+        <v>3.630239520958084</v>
       </c>
       <c r="FF5" t="n">
-        <v>4.71377245508982</v>
+        <v>7.630239520958083</v>
       </c>
       <c r="FG5" t="n">
-        <v>28.28263473053892</v>
+        <v>43.74670658682634</v>
       </c>
       <c r="FH5" t="n">
-        <v>10.01676646706587</v>
+        <v>13.22574850299401</v>
       </c>
       <c r="FI5" t="n">
-        <v>160.2682634730539</v>
+        <v>157.6916167664671</v>
       </c>
       <c r="FJ5" t="n">
-        <v>33.58562874251497</v>
+        <v>31.02964071856287</v>
       </c>
       <c r="FK5" t="n">
-        <v>12.37365269461078</v>
+        <v>17.80389221556886</v>
       </c>
       <c r="FL5" t="n">
-        <v>42.42395209580838</v>
+        <v>56.46377245508982</v>
       </c>
       <c r="FM5" t="n">
-        <v>1920.862275449102</v>
+        <v>1702.560778443114</v>
       </c>
       <c r="FN5" t="n">
-        <v>45.95928143712575</v>
+        <v>39.67724550898203</v>
       </c>
       <c r="FO5" t="n">
-        <v>28.28263473053892</v>
+        <v>24.92544910179641</v>
       </c>
       <c r="FP5" t="n">
-        <v>29.46107784431138</v>
+        <v>42.72934131736527</v>
       </c>
       <c r="FQ5" t="n">
-        <v>67.76047904191616</v>
+        <v>51.88562874251497</v>
       </c>
       <c r="FR5" t="n">
-        <v>5.302994011976048</v>
+        <v>4.069461077844312</v>
       </c>
       <c r="FS5" t="n">
-        <v>21.21197604790419</v>
+        <v>14.24311377245509</v>
       </c>
       <c r="FT5" t="n">
-        <v>55.97604790419161</v>
+        <v>46.29011976047904</v>
       </c>
       <c r="FU5" t="n">
-        <v>154.3760479041916</v>
+        <v>133.2748502994012</v>
       </c>
       <c r="FV5" t="n">
-        <v>1599.147305389221</v>
+        <v>1426.346107784431</v>
       </c>
       <c r="FW5" t="n">
-        <v>1331.640718562874</v>
+        <v>1181.669760479042</v>
       </c>
       <c r="FX5" t="n">
-        <v>244.0555688622754</v>
+        <v>209.9333233532934</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.3904107868179724</v>
+        <v>0.4649800244711815</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.091227335538713</v>
+        <v>0.8237351458074563</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3643860941219166</v>
+        <v>0.3447737857618097</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.9155165604619636</v>
+        <v>0.7573719228210247</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.07922325230038278</v>
+        <v>0.101599213931971</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3022810937262667</v>
+        <v>0.2441499264347711</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.440555688622754</v>
+        <v>2.099333233532934</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.699926948242552</v>
+        <v>1.501671280535132</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.1689407963236907</v>
+        <v>0.1993169630984744</v>
       </c>
       <c r="GH5" t="n">
-        <v>1.605130390217157</v>
+        <v>1.576882529541789</v>
       </c>
       <c r="GI5" t="n">
-        <v>1.571986518012813</v>
+        <v>1.50239061909929</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.1030105350416986</v>
+        <v>0.1329370630219796</v>
       </c>
       <c r="GK5" t="n">
-        <v>-2.47065868263473</v>
+        <v>-1.804491017964071</v>
       </c>
       <c r="GL5" t="n">
-        <v>-1.365269461077844</v>
+        <v>6.743113772455096</v>
       </c>
       <c r="GM5" t="n">
-        <v>1.198802395209581</v>
+        <v>1.662275449101795</v>
       </c>
       <c r="GN5" t="n">
-        <v>-25.12065868263471</v>
+        <v>-0.3964071856287319</v>
       </c>
       <c r="GO5" t="n">
-        <v>4.547305389221556</v>
+        <v>6.514071856287423</v>
       </c>
       <c r="GP5" t="n">
-        <v>2.206586826347307</v>
+        <v>4.851796407185631</v>
       </c>
       <c r="GQ5" t="n">
-        <v>3.55988023952095</v>
+        <v>14.09251497005989</v>
       </c>
       <c r="GR5" t="n">
-        <v>-334.9808383233531</v>
+        <v>235.4715568862275</v>
       </c>
       <c r="GS5" t="n">
-        <v>2.267664670658682</v>
+        <v>17.93293413173654</v>
       </c>
       <c r="GT5" t="n">
-        <v>-4.729940119760478</v>
+        <v>13.26556886227545</v>
       </c>
       <c r="GU5" t="n">
-        <v>3.624850299401203</v>
+        <v>-11.01137724550898</v>
       </c>
       <c r="GV5" t="n">
-        <v>-0.467065868263461</v>
+        <v>12.84491017964072</v>
       </c>
       <c r="GW5" t="n">
-        <v>-1.377544910179641</v>
+        <v>0.4616766467065858</v>
       </c>
       <c r="GX5" t="n">
-        <v>-3.267065868263472</v>
+        <v>8.412574850299404</v>
       </c>
       <c r="GY5" t="n">
-        <v>-8.30988023952095</v>
+        <v>-3.567964071856281</v>
       </c>
       <c r="GZ5" t="n">
-        <v>25.07305389221557</v>
+        <v>34.37724550898204</v>
       </c>
       <c r="HA5" t="n">
-        <v>-283.0002994011973</v>
+        <v>141.4275449101797</v>
       </c>
       <c r="HB5" t="n">
-        <v>-263.3577844311376</v>
+        <v>105.1733532934131</v>
       </c>
       <c r="HC5" t="n">
-        <v>-18.79086826347304</v>
+        <v>55.97973053892215</v>
       </c>
       <c r="HD5" t="n">
-        <v>-0.1077962539788887</v>
+        <v>0.03351952814771869</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.0703851537683875</v>
+        <v>0.1722268278419014</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.04518244736653509</v>
+        <v>-0.0855714112899742</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.2293033875540923</v>
+        <v>0.4877335372544951</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.01691406704713093</v>
+        <v>0.03728961590321467</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.09119606738003994</v>
+        <v>0.09978965763213582</v>
       </c>
       <c r="HJ5" t="n">
-        <v>-0.1879086826347307</v>
+        <v>0.5597973053892216</v>
       </c>
       <c r="HK5" t="n">
-        <v>-0.3143568491245485</v>
+        <v>-0.1399336725925708</v>
       </c>
       <c r="HL5" t="n">
-        <v>-0.02332579658391823</v>
+        <v>-0.01392838638053151</v>
       </c>
       <c r="HM5" t="n">
-        <v>-0.2501488633187265</v>
+        <v>-0.008495056875708062</v>
       </c>
       <c r="HN5" t="n">
-        <v>-0.2218285099971937</v>
+        <v>0.07851115046027934</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.0231873065331543</v>
+        <v>0.04856327906772537</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>3.630239520958084</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.581736526946108</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>43.03443113772455</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>12.15089820359282</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>152.8988023952096</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>31.89610778443114</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>17.72005988023952</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>55.69161676646707</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1713.782934131737</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>35.44011976047904</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>27.33952095808383</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>42.02185628742515</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>51.64131736526946</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>4.050299401197605</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>17.21377245508982</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>46.07215568862276</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>141.7604790419162</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>1446.463173652695</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1193.319461077844</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>208.1347604790419</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0.4094971821063755</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.7695237955461627</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0.3712774451097804</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0.6975515635395875</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0.09849634241249287</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>0.2536687855767008</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.081347604790419</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.470647049278496</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0.1761106729002249</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.525409224007145</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>1.459034604266673</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>0.1292072229908692</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER6" t="n">
-        <v>1</v>
-      </c>
-      <c r="ES6" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="FD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE6" t="n">
-        <v>2.664670658682635</v>
-      </c>
-      <c r="FF6" t="n">
-        <v>5.994011976047903</v>
-      </c>
-      <c r="FG6" t="n">
-        <v>32.96706586826347</v>
-      </c>
-      <c r="FH6" t="n">
-        <v>14.38562874251497</v>
-      </c>
-      <c r="FI6" t="n">
-        <v>119.2808383233533</v>
-      </c>
-      <c r="FJ6" t="n">
-        <v>34.76526946107784</v>
-      </c>
-      <c r="FK6" t="n">
-        <v>11.98802395209581</v>
-      </c>
-      <c r="FL6" t="n">
-        <v>37.162874251497</v>
-      </c>
-      <c r="FM6" t="n">
-        <v>1553.647904191617</v>
-      </c>
-      <c r="FN6" t="n">
-        <v>50.94910179640718</v>
-      </c>
-      <c r="FO6" t="n">
-        <v>19.18083832335329</v>
-      </c>
-      <c r="FP6" t="n">
-        <v>32.36766467065868</v>
-      </c>
-      <c r="FQ6" t="n">
-        <v>94.10598802395208</v>
-      </c>
-      <c r="FR6" t="n">
-        <v>4.795209580838323</v>
-      </c>
-      <c r="FS6" t="n">
-        <v>24.5754491017964</v>
-      </c>
-      <c r="FT6" t="n">
-        <v>41.35868263473053</v>
-      </c>
-      <c r="FU6" t="n">
-        <v>173.2269461077844</v>
-      </c>
-      <c r="FV6" t="n">
-        <v>1188.612574850299</v>
-      </c>
-      <c r="FW6" t="n">
-        <v>948.8520958083832</v>
-      </c>
-      <c r="FX6" t="n">
-        <v>238.3219161676647</v>
-      </c>
-      <c r="FY6" t="n">
-        <v>0.5704406872529449</v>
-      </c>
-      <c r="FZ6" t="n">
-        <v>1.331791710696254</v>
-      </c>
-      <c r="GA6" t="n">
-        <v>0.4434963406520291</v>
-      </c>
-      <c r="GB6" t="n">
-        <v>0.7937874251497005</v>
-      </c>
-      <c r="GC6" t="n">
-        <v>0.09556278852672591</v>
-      </c>
-      <c r="GD6" t="n">
-        <v>0.4408580848927447</v>
-      </c>
-      <c r="GE6" t="n">
-        <v>2.383219161676646</v>
-      </c>
-      <c r="GF6" t="n">
-        <v>1.518263473053892</v>
-      </c>
-      <c r="GG6" t="n">
-        <v>0.1157476196730993</v>
-      </c>
-      <c r="GH6" t="n">
-        <v>1.188763481600605</v>
-      </c>
-      <c r="GI6" t="n">
-        <v>1.249018596261744</v>
-      </c>
-      <c r="GJ6" t="n">
-        <v>0.1267729423179457</v>
-      </c>
-      <c r="GK6" t="n">
-        <v>0.587724550898205</v>
-      </c>
-      <c r="GL6" t="n">
-        <v>10.06736526946109</v>
-      </c>
-      <c r="GM6" t="n">
-        <v>-2.234730538922152</v>
-      </c>
-      <c r="GN6" t="n">
-        <v>33.61796407185631</v>
-      </c>
-      <c r="GO6" t="n">
-        <v>-2.869161676646698</v>
-      </c>
-      <c r="GP6" t="n">
-        <v>5.732035928143715</v>
-      </c>
-      <c r="GQ6" t="n">
-        <v>18.52874251497007</v>
-      </c>
-      <c r="GR6" t="n">
-        <v>160.1350299401199</v>
-      </c>
-      <c r="GS6" t="n">
-        <v>-15.50898203592813</v>
-      </c>
-      <c r="GT6" t="n">
-        <v>8.158682634730543</v>
-      </c>
-      <c r="GU6" t="n">
-        <v>9.654191616766468</v>
-      </c>
-      <c r="GV6" t="n">
-        <v>-42.46467065868262</v>
-      </c>
-      <c r="GW6" t="n">
-        <v>-0.7449101796407183</v>
-      </c>
-      <c r="GX6" t="n">
-        <v>-7.361676646706581</v>
-      </c>
-      <c r="GY6" t="n">
-        <v>4.713473053892223</v>
-      </c>
-      <c r="GZ6" t="n">
-        <v>-31.46646706586822</v>
-      </c>
-      <c r="HA6" t="n">
-        <v>257.8505988023953</v>
-      </c>
-      <c r="HB6" t="n">
-        <v>244.4673652694612</v>
-      </c>
-      <c r="HC6" t="n">
-        <v>-30.18715568862277</v>
-      </c>
-      <c r="HD6" t="n">
-        <v>-0.1609435051465694</v>
-      </c>
-      <c r="HE6" t="n">
-        <v>-0.5622679151500918</v>
-      </c>
-      <c r="HF6" t="n">
-        <v>-0.0722188955422487</v>
-      </c>
-      <c r="HG6" t="n">
-        <v>-0.09623586161011299</v>
-      </c>
-      <c r="HH6" t="n">
-        <v>0.002933553885766965</v>
-      </c>
-      <c r="HI6" t="n">
-        <v>-0.1871892993160439</v>
-      </c>
-      <c r="HJ6" t="n">
-        <v>-0.3018715568862271</v>
-      </c>
-      <c r="HK6" t="n">
-        <v>-0.04761642377539599</v>
-      </c>
-      <c r="HL6" t="n">
-        <v>0.06036305322712564</v>
-      </c>
-      <c r="HM6" t="n">
-        <v>0.3366457424065401</v>
-      </c>
-      <c r="HN6" t="n">
-        <v>0.2100160080049294</v>
-      </c>
-      <c r="HO6" t="n">
-        <v>0.002434280672923533</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr"/>
+      <c r="DQ6" t="inlineStr"/>
+      <c r="DR6" t="inlineStr"/>
+      <c r="DS6" t="inlineStr"/>
+      <c r="DT6" t="inlineStr"/>
+      <c r="DU6" t="inlineStr"/>
+      <c r="DV6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr"/>
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr"/>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
+      <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr"/>
+      <c r="EQ6" t="inlineStr"/>
+      <c r="ER6" t="inlineStr"/>
+      <c r="ES6" t="inlineStr"/>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
+      <c r="EZ6" t="inlineStr"/>
+      <c r="FA6" t="inlineStr"/>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+      <c r="FF6" t="inlineStr"/>
+      <c r="FG6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr"/>
+      <c r="FM6" t="inlineStr"/>
+      <c r="FN6" t="inlineStr"/>
+      <c r="FO6" t="inlineStr"/>
+      <c r="FP6" t="inlineStr"/>
+      <c r="FQ6" t="inlineStr"/>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+      <c r="FT6" t="inlineStr"/>
+      <c r="FU6" t="inlineStr"/>
+      <c r="FV6" t="inlineStr"/>
+      <c r="FW6" t="inlineStr"/>
+      <c r="FX6" t="inlineStr"/>
+      <c r="FY6" t="inlineStr"/>
+      <c r="FZ6" t="inlineStr"/>
+      <c r="GA6" t="inlineStr"/>
+      <c r="GB6" t="inlineStr"/>
+      <c r="GC6" t="inlineStr"/>
+      <c r="GD6" t="inlineStr"/>
+      <c r="GE6" t="inlineStr"/>
+      <c r="GF6" t="inlineStr"/>
+      <c r="GG6" t="inlineStr"/>
+      <c r="GH6" t="inlineStr"/>
+      <c r="GI6" t="inlineStr"/>
+      <c r="GJ6" t="inlineStr"/>
+      <c r="GK6" t="inlineStr"/>
+      <c r="GL6" t="inlineStr"/>
+      <c r="GM6" t="inlineStr"/>
+      <c r="GN6" t="inlineStr"/>
+      <c r="GO6" t="inlineStr"/>
+      <c r="GP6" t="inlineStr"/>
+      <c r="GQ6" t="inlineStr"/>
+      <c r="GR6" t="inlineStr"/>
+      <c r="GS6" t="inlineStr"/>
+      <c r="GT6" t="inlineStr"/>
+      <c r="GU6" t="inlineStr"/>
+      <c r="GV6" t="inlineStr"/>
+      <c r="GW6" t="inlineStr"/>
+      <c r="GX6" t="inlineStr"/>
+      <c r="GY6" t="inlineStr"/>
+      <c r="GZ6" t="inlineStr"/>
+      <c r="HA6" t="inlineStr"/>
+      <c r="HB6" t="inlineStr"/>
+      <c r="HC6" t="inlineStr"/>
+      <c r="HD6" t="inlineStr"/>
+      <c r="HE6" t="inlineStr"/>
+      <c r="HF6" t="inlineStr"/>
+      <c r="HG6" t="inlineStr"/>
+      <c r="HH6" t="inlineStr"/>
+      <c r="HI6" t="inlineStr"/>
+      <c r="HJ6" t="inlineStr"/>
+      <c r="HK6" t="inlineStr"/>
+      <c r="HL6" t="inlineStr"/>
+      <c r="HM6" t="inlineStr"/>
+      <c r="HN6" t="inlineStr"/>
+      <c r="HO6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="inlineStr"/>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
-      <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="inlineStr"/>
-      <c r="DG7" t="inlineStr"/>
-      <c r="DH7" t="inlineStr"/>
-      <c r="DI7" t="inlineStr"/>
-      <c r="DJ7" t="inlineStr"/>
-      <c r="DK7" t="inlineStr"/>
-      <c r="DL7" t="inlineStr"/>
-      <c r="DM7" t="inlineStr"/>
-      <c r="DN7" t="inlineStr"/>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
-      <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
-      <c r="DT7" t="inlineStr"/>
-      <c r="DU7" t="inlineStr"/>
-      <c r="DV7" t="inlineStr"/>
-      <c r="DW7" t="inlineStr"/>
-      <c r="DX7" t="inlineStr"/>
-      <c r="DY7" t="inlineStr"/>
-      <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="inlineStr"/>
-      <c r="EB7" t="inlineStr"/>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
-      <c r="EE7" t="inlineStr"/>
-      <c r="EF7" t="inlineStr"/>
-      <c r="EG7" t="inlineStr"/>
-      <c r="EH7" t="inlineStr"/>
-      <c r="EI7" t="inlineStr"/>
-      <c r="EJ7" t="inlineStr"/>
-      <c r="EK7" t="inlineStr"/>
-      <c r="EL7" t="inlineStr"/>
-      <c r="EM7" t="inlineStr"/>
-      <c r="EN7" t="inlineStr"/>
-      <c r="EO7" t="inlineStr"/>
-      <c r="EP7" t="inlineStr"/>
-      <c r="EQ7" t="inlineStr"/>
-      <c r="ER7" t="inlineStr"/>
-      <c r="ES7" t="inlineStr"/>
-      <c r="ET7" t="inlineStr"/>
-      <c r="EU7" t="inlineStr"/>
-      <c r="EV7" t="inlineStr"/>
-      <c r="EW7" t="inlineStr"/>
-      <c r="EX7" t="inlineStr"/>
-      <c r="EY7" t="inlineStr"/>
-      <c r="EZ7" t="inlineStr"/>
-      <c r="FA7" t="inlineStr"/>
-      <c r="FB7" t="inlineStr"/>
-      <c r="FC7" t="inlineStr"/>
-      <c r="FD7" t="inlineStr"/>
-      <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr"/>
-      <c r="FG7" t="inlineStr"/>
-      <c r="FH7" t="inlineStr"/>
-      <c r="FI7" t="inlineStr"/>
-      <c r="FJ7" t="inlineStr"/>
-      <c r="FK7" t="inlineStr"/>
-      <c r="FL7" t="inlineStr"/>
-      <c r="FM7" t="inlineStr"/>
-      <c r="FN7" t="inlineStr"/>
-      <c r="FO7" t="inlineStr"/>
-      <c r="FP7" t="inlineStr"/>
-      <c r="FQ7" t="inlineStr"/>
-      <c r="FR7" t="inlineStr"/>
-      <c r="FS7" t="inlineStr"/>
-      <c r="FT7" t="inlineStr"/>
-      <c r="FU7" t="inlineStr"/>
-      <c r="FV7" t="inlineStr"/>
-      <c r="FW7" t="inlineStr"/>
-      <c r="FX7" t="inlineStr"/>
-      <c r="FY7" t="inlineStr"/>
-      <c r="FZ7" t="inlineStr"/>
-      <c r="GA7" t="inlineStr"/>
-      <c r="GB7" t="inlineStr"/>
-      <c r="GC7" t="inlineStr"/>
-      <c r="GD7" t="inlineStr"/>
-      <c r="GE7" t="inlineStr"/>
-      <c r="GF7" t="inlineStr"/>
-      <c r="GG7" t="inlineStr"/>
-      <c r="GH7" t="inlineStr"/>
-      <c r="GI7" t="inlineStr"/>
-      <c r="GJ7" t="inlineStr"/>
-      <c r="GK7" t="inlineStr"/>
-      <c r="GL7" t="inlineStr"/>
-      <c r="GM7" t="inlineStr"/>
-      <c r="GN7" t="inlineStr"/>
-      <c r="GO7" t="inlineStr"/>
-      <c r="GP7" t="inlineStr"/>
-      <c r="GQ7" t="inlineStr"/>
-      <c r="GR7" t="inlineStr"/>
-      <c r="GS7" t="inlineStr"/>
-      <c r="GT7" t="inlineStr"/>
-      <c r="GU7" t="inlineStr"/>
-      <c r="GV7" t="inlineStr"/>
-      <c r="GW7" t="inlineStr"/>
-      <c r="GX7" t="inlineStr"/>
-      <c r="GY7" t="inlineStr"/>
-      <c r="GZ7" t="inlineStr"/>
-      <c r="HA7" t="inlineStr"/>
-      <c r="HB7" t="inlineStr"/>
-      <c r="HC7" t="inlineStr"/>
-      <c r="HD7" t="inlineStr"/>
-      <c r="HE7" t="inlineStr"/>
-      <c r="HF7" t="inlineStr"/>
-      <c r="HG7" t="inlineStr"/>
-      <c r="HH7" t="inlineStr"/>
-      <c r="HI7" t="inlineStr"/>
-      <c r="HJ7" t="inlineStr"/>
-      <c r="HK7" t="inlineStr"/>
-      <c r="HL7" t="inlineStr"/>
-      <c r="HM7" t="inlineStr"/>
-      <c r="HN7" t="inlineStr"/>
-      <c r="HO7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.375748502994012</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.368862275449103</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>27.30538922155689</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>8.191616766467067</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>157.8251497005988</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>32.76646706586827</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>14.19880239520958</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>46.41916167664671</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1861.135329341318</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>43.68862275449102</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>25.12095808383233</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>32.76646706586827</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>58.97964071856288</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>5.461077844311378</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>21.29820359281437</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>62.25628742514971</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>141.4419161676647</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1568.967664670659</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1304.651497005988</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>225.8701796407186</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.346568401658222</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.8891754951635192</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.3984023397056156</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.727170258413654</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.08086423885090145</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.2616213496196114</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.258701796407186</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.549842859735076</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1716148490069616</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.578177061852924</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1.516218717422022</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.1063420305024728</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>1.826347305389222</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>1.69311377245509</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>25.39670658682635</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>5.6437125748503</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>119.6467065868264</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>31.04041916167665</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>9.594311377245509</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>44.02095808383233</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>1573.467065868264</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>51.35778443113772</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>19.18862275449102</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>19.75299401197605</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>63.77395209580839</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>3.38622754491018</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>23.70359281437126</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>36.11976047904192</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>165.9251497005988</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>1272.657185628743</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>1054.245508982036</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>228.9654191616766</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.151170872540633</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.5782973015008943</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.3857061239839162</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>1.117385880413087</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.1048951690478497</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.398356508858096</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>2.289654191616767</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>1.090296589360961</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.1213035388109362</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>1.202682461646357</v>
+      </c>
+      <c r="GI7" t="n">
+        <v>1.237964261833874</v>
+      </c>
+      <c r="GJ7" t="n">
+        <v>0.1252751327937485</v>
+      </c>
+      <c r="GK7" t="n">
+        <v>2.675748502994013</v>
+      </c>
+      <c r="GL7" t="n">
+        <v>1.908682634730539</v>
+      </c>
+      <c r="GM7" t="n">
+        <v>2.547904191616768</v>
+      </c>
+      <c r="GN7" t="n">
+        <v>38.17844311377246</v>
+      </c>
+      <c r="GO7" t="n">
+        <v>1.726047904191621</v>
+      </c>
+      <c r="GP7" t="n">
+        <v>4.604491017964074</v>
+      </c>
+      <c r="GQ7" t="n">
+        <v>2.398203592814376</v>
+      </c>
+      <c r="GR7" t="n">
+        <v>287.6682634730539</v>
+      </c>
+      <c r="GS7" t="n">
+        <v>-7.669161676646702</v>
+      </c>
+      <c r="GT7" t="n">
+        <v>5.932335329341317</v>
+      </c>
+      <c r="GU7" t="n">
+        <v>13.01347305389222</v>
+      </c>
+      <c r="GV7" t="n">
+        <v>-4.794311377245506</v>
+      </c>
+      <c r="GW7" t="n">
+        <v>2.074850299401198</v>
+      </c>
+      <c r="GX7" t="n">
+        <v>-2.405389221556888</v>
+      </c>
+      <c r="GY7" t="n">
+        <v>26.13652694610779</v>
+      </c>
+      <c r="GZ7" t="n">
+        <v>-24.48323353293412</v>
+      </c>
+      <c r="HA7" t="n">
+        <v>296.3104790419163</v>
+      </c>
+      <c r="HB7" t="n">
+        <v>250.4059880239522</v>
+      </c>
+      <c r="HC7" t="n">
+        <v>-3.095239520958017</v>
+      </c>
+      <c r="HD7" t="n">
+        <v>0.195397529117589</v>
+      </c>
+      <c r="HE7" t="n">
+        <v>0.3108781936626249</v>
+      </c>
+      <c r="HF7" t="n">
+        <v>0.01269621572169932</v>
+      </c>
+      <c r="HG7" t="n">
+        <v>-0.3902156219994327</v>
+      </c>
+      <c r="HH7" t="n">
+        <v>-0.02403093019694824</v>
+      </c>
+      <c r="HI7" t="n">
+        <v>-0.1367351592384846</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>-0.03095239520958115</v>
+      </c>
+      <c r="HK7" t="n">
+        <v>0.4595462703741149</v>
+      </c>
+      <c r="HL7" t="n">
+        <v>0.05031131019602549</v>
+      </c>
+      <c r="HM7" t="n">
+        <v>0.3754946002065667</v>
+      </c>
+      <c r="HN7" t="n">
+        <v>0.2782544555881485</v>
+      </c>
+      <c r="HO7" t="n">
+        <v>-0.01893310229127569</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -5151,25 +5151,25 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -5178,28 +5178,28 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
         <v>1</v>
@@ -5223,31 +5223,31 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
@@ -5271,16 +5271,16 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -5298,124 +5298,124 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.826347305389222</v>
+        <v>2.290419161676647</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.761377245508982</v>
+        <v>2.453892215568863</v>
       </c>
       <c r="BO8" t="n">
-        <v>28.18203592814372</v>
+        <v>29.44670658682635</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.697005988023952</v>
+        <v>11.6559880239521</v>
       </c>
       <c r="BQ8" t="n">
-        <v>109.7925149700599</v>
+        <v>130.0562874251497</v>
       </c>
       <c r="BR8" t="n">
-        <v>32.29191616766467</v>
+        <v>39.87574850299401</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.15538922155689</v>
+        <v>14.72335329341317</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.97005988023952</v>
+        <v>44.17005988023953</v>
       </c>
       <c r="BU8" t="n">
-        <v>1471.337125748503</v>
+        <v>1539.817365269461</v>
       </c>
       <c r="BV8" t="n">
-        <v>51.07994011976048</v>
+        <v>58.27994011976048</v>
       </c>
       <c r="BW8" t="n">
-        <v>22.89790419161677</v>
+        <v>33.74101796407186</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.89790419161677</v>
+        <v>38.03532934131737</v>
       </c>
       <c r="BY8" t="n">
-        <v>72.80359281437127</v>
+        <v>79.13802395209582</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.522754491017964</v>
+        <v>4.294311377245509</v>
       </c>
       <c r="CA8" t="n">
-        <v>23.48502994011976</v>
+        <v>19.6311377245509</v>
       </c>
       <c r="CB8" t="n">
-        <v>41.09880239520958</v>
+        <v>46.01047904191617</v>
       </c>
       <c r="CC8" t="n">
-        <v>176.7248502994012</v>
+        <v>188.3362275449102</v>
       </c>
       <c r="CD8" t="n">
-        <v>1157.224850299401</v>
+        <v>1206.701497005988</v>
       </c>
       <c r="CE8" t="n">
-        <v>922.9616766467066</v>
+        <v>932.4790419161677</v>
       </c>
       <c r="CF8" t="n">
-        <v>227.9222155688623</v>
+        <v>235.5736526946108</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.1372501749747259</v>
+        <v>0.3091709438266325</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.414800528812505</v>
+        <v>1.202601938979185</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.4427710819366639</v>
+        <v>0.4547958889912483</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.073478535479967</v>
+        <v>1.218687816674344</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.1285390475780213</v>
+        <v>0.1085343841422472</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.4843015807197282</v>
+        <v>0.4849370829812454</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.279222155688623</v>
+        <v>2.355736526946108</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.111673737384815</v>
+        <v>1.501610752853268</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1147588564780721</v>
+        <v>0.1699742005975694</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.103173626536932</v>
+        <v>1.304494281022376</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.174449088737302</v>
+        <v>1.345383078532697</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.157559649269349</v>
+        <v>0.1452313847223725</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT8" t="n">
         <v>1</v>
@@ -5424,16 +5424,16 @@
         <v>1</v>
       </c>
       <c r="CV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>
@@ -5442,10 +5442,10 @@
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>1</v>
@@ -5460,10 +5460,10 @@
         <v>1</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
         <v>1</v>
@@ -5472,13 +5472,13 @@
         <v>1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="DS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -5502,10 +5502,10 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
         <v>1</v>
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="EA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB8" t="n">
         <v>1</v>
@@ -5526,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="ED8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>1</v>
@@ -5547,10 +5547,10 @@
         <v>1</v>
       </c>
       <c r="EK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -5562,238 +5562,238 @@
         <v>1</v>
       </c>
       <c r="EP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV8" t="n">
         <v>1</v>
       </c>
       <c r="EW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY8" t="n">
         <v>0</v>
       </c>
       <c r="EZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>1.736526946107784</v>
+        <v>2.664670658682635</v>
       </c>
       <c r="FF8" t="n">
-        <v>2.495808383233533</v>
+        <v>6.290419161676647</v>
       </c>
       <c r="FG8" t="n">
-        <v>24.33413173652695</v>
+        <v>34.59730538922156</v>
       </c>
       <c r="FH8" t="n">
-        <v>8.735329341317366</v>
+        <v>13.83892215568862</v>
       </c>
       <c r="FI8" t="n">
-        <v>98.58443113772455</v>
+        <v>119.5179640718563</v>
       </c>
       <c r="FJ8" t="n">
-        <v>31.82155688622754</v>
+        <v>32.0811377245509</v>
       </c>
       <c r="FK8" t="n">
-        <v>8.735329341317366</v>
+        <v>15.09700598802395</v>
       </c>
       <c r="FL8" t="n">
-        <v>38.68502994011976</v>
+        <v>42.14580838323354</v>
       </c>
       <c r="FM8" t="n">
-        <v>1365.207185628743</v>
+        <v>1556.249700598803</v>
       </c>
       <c r="FN8" t="n">
-        <v>63.0191616766467</v>
+        <v>53.4685628742515</v>
       </c>
       <c r="FO8" t="n">
-        <v>22.4622754491018</v>
+        <v>27.67784431137725</v>
       </c>
       <c r="FP8" t="n">
-        <v>22.4622754491018</v>
+        <v>39.00059880239522</v>
       </c>
       <c r="FQ8" t="n">
-        <v>84.23353293413174</v>
+        <v>103.162874251497</v>
       </c>
       <c r="FR8" t="n">
-        <v>6.239520958083832</v>
+        <v>6.290419161676647</v>
       </c>
       <c r="FS8" t="n">
-        <v>36.18922155688622</v>
+        <v>26.41976047904192</v>
       </c>
       <c r="FT8" t="n">
-        <v>38.06107784431138</v>
+        <v>36.48443113772455</v>
       </c>
       <c r="FU8" t="n">
-        <v>168.4670658682635</v>
+        <v>184.9383233532934</v>
       </c>
       <c r="FV8" t="n">
-        <v>1023.281437125749</v>
+        <v>1162.469461077844</v>
       </c>
       <c r="FW8" t="n">
-        <v>798.0347305389222</v>
+        <v>913.997904191617</v>
       </c>
       <c r="FX8" t="n">
-        <v>240.0967664670659</v>
+        <v>244.4456886227545</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.3899700598802395</v>
+        <v>0.5986492926665524</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.9863242745278672</v>
+        <v>1.257862450062168</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1767864271457086</v>
+        <v>0.4792222572399062</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.8912727486204062</v>
+        <v>0.8606302071969423</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1113300457087132</v>
+        <v>0.1202639773323842</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.5368207723312444</v>
+        <v>0.5181066043320884</v>
       </c>
       <c r="GE8" t="n">
-        <v>2.400967664670659</v>
+        <v>2.444456886227545</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.415673129265943</v>
+        <v>1.677214691496129</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.1125530186925061</v>
+        <v>0.1338510326931569</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.9821998342254254</v>
+        <v>1.186998717377929</v>
       </c>
       <c r="GI8" t="n">
-        <v>1.096582605676712</v>
+        <v>1.268788537631564</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.135556067614019</v>
+        <v>0.1641608052510273</v>
       </c>
       <c r="GK8" t="n">
-        <v>-0.7344311377245509</v>
+        <v>-3.836526946107785</v>
       </c>
       <c r="GL8" t="n">
-        <v>3.84790419161677</v>
+        <v>-5.150598802395212</v>
       </c>
       <c r="GM8" t="n">
-        <v>-4.038323353293413</v>
+        <v>-2.182934131736529</v>
       </c>
       <c r="GN8" t="n">
-        <v>11.20808383233533</v>
+        <v>10.53832335329339</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.4703592814371298</v>
+        <v>7.794610778443115</v>
       </c>
       <c r="GP8" t="n">
-        <v>2.420059880239521</v>
+        <v>-0.3736526946107777</v>
       </c>
       <c r="GQ8" t="n">
-        <v>8.285029940119763</v>
+        <v>2.024251497005991</v>
       </c>
       <c r="GR8" t="n">
-        <v>106.1299401197605</v>
+        <v>-16.43233532934141</v>
       </c>
       <c r="GS8" t="n">
-        <v>-11.93922155688622</v>
+        <v>4.811377245508979</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.4356287425149716</v>
+        <v>6.063173652694609</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.4356287425149716</v>
+        <v>-0.9652694610778454</v>
       </c>
       <c r="GV8" t="n">
-        <v>-11.42994011976047</v>
+        <v>-24.02485029940118</v>
       </c>
       <c r="GW8" t="n">
-        <v>-2.716766467065868</v>
+        <v>-1.996107784431138</v>
       </c>
       <c r="GX8" t="n">
-        <v>-12.70419161676646</v>
+        <v>-6.788622754491019</v>
       </c>
       <c r="GY8" t="n">
-        <v>3.037724550898204</v>
+        <v>9.526047904191621</v>
       </c>
       <c r="GZ8" t="n">
-        <v>8.257784431137736</v>
+        <v>3.39790419161676</v>
       </c>
       <c r="HA8" t="n">
-        <v>133.9434131736526</v>
+        <v>44.23203592814366</v>
       </c>
       <c r="HB8" t="n">
-        <v>124.9269461077844</v>
+        <v>18.48113772455076</v>
       </c>
       <c r="HC8" t="n">
-        <v>-12.17455089820356</v>
+        <v>-8.872035928143731</v>
       </c>
       <c r="HD8" t="n">
-        <v>-0.2527198849055137</v>
+        <v>-0.28947834883992</v>
       </c>
       <c r="HE8" t="n">
-        <v>-0.5715237457153622</v>
+        <v>-0.05526051108298358</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.2659846547909553</v>
+        <v>-0.0244263682486579</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.1822057868595612</v>
+        <v>0.3580576094774015</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.01720900186930818</v>
+        <v>-0.01172959319013696</v>
       </c>
       <c r="HI8" t="n">
-        <v>-0.05251919161151619</v>
+        <v>-0.033169521350843</v>
       </c>
       <c r="HJ8" t="n">
-        <v>-0.1217455089820363</v>
+        <v>-0.08872035928143696</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.3039993918811281</v>
+        <v>-0.1756039386428607</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.002205837785566045</v>
+        <v>0.0361231679044125</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.1209737923115068</v>
+        <v>0.1174955636444475</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.07786648306059019</v>
+        <v>0.07659454090113282</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.02200358165532998</v>
+        <v>-0.01892942052865479</v>
       </c>
     </row>
     <row r="9">
@@ -5801,13 +5801,13 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -5816,25 +5816,25 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -5843,52 +5843,52 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>1</v>
@@ -5903,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -5921,16 +5921,16 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
@@ -5939,19 +5939,19 @@
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
         <v>1</v>
@@ -5972,13 +5972,13 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -5987,103 +5987,103 @@
         <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>5</v>
+        <v>1.833832335329341</v>
       </c>
       <c r="BN9" t="n">
-        <v>6</v>
+        <v>4.826347305389222</v>
       </c>
       <c r="BO9" t="n">
-        <v>31.2</v>
+        <v>34.38772455089821</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.6</v>
+        <v>13.27245508982036</v>
       </c>
       <c r="BQ9" t="n">
-        <v>145.2</v>
+        <v>136.9476047904191</v>
       </c>
       <c r="BR9" t="n">
-        <v>16.4</v>
+        <v>41.02395209580838</v>
       </c>
       <c r="BS9" t="n">
-        <v>14</v>
+        <v>10.2559880239521</v>
       </c>
       <c r="BT9" t="n">
-        <v>32</v>
+        <v>71.18862275449102</v>
       </c>
       <c r="BU9" t="n">
-        <v>1840.8</v>
+        <v>1669.916167664671</v>
       </c>
       <c r="BV9" t="n">
-        <v>31.6</v>
+        <v>47.05688622754491</v>
       </c>
       <c r="BW9" t="n">
-        <v>14</v>
+        <v>25.33832335329341</v>
       </c>
       <c r="BX9" t="n">
-        <v>12.4</v>
+        <v>38.61077844311377</v>
       </c>
       <c r="BY9" t="n">
-        <v>19.6</v>
+        <v>71.79191616766467</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.2</v>
+        <v>3.016467065868263</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>21.11526946107784</v>
       </c>
       <c r="CB9" t="n">
-        <v>27.6</v>
+        <v>60.93263473053891</v>
       </c>
       <c r="CC9" t="n">
-        <v>96.40000000000001</v>
+        <v>199.690119760479</v>
       </c>
       <c r="CD9" t="n">
-        <v>1638</v>
+        <v>1367.062874251497</v>
       </c>
       <c r="CE9" t="n">
-        <v>1497.6</v>
+        <v>1085.928143712575</v>
       </c>
       <c r="CF9" t="n">
-        <v>182.72</v>
+        <v>236.0687125748503</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.4981818181818182</v>
+        <v>0.4776072854291417</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.8581818181818182</v>
+        <v>1.157988190286094</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1938949938949939</v>
+        <v>0.7432331765041346</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.4459096459096459</v>
+        <v>1.418347234103222</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.03884470223695138</v>
+        <v>0.1581581616565504</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.1195923353392955</v>
+        <v>0.4668535830410516</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.8272</v>
+        <v>2.360687125748503</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.972063492063492</v>
+        <v>1.50388267216419</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.1589984418779085</v>
+        <v>0.1391936186262608</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.455510379292969</v>
+        <v>1.372845548260429</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.375436216151886</v>
+        <v>1.393282434650794</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.05539645098296839</v>
+        <v>0.1812102884501308</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -6098,16 +6098,16 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -6116,16 +6116,16 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
         <v>1</v>
@@ -6134,25 +6134,25 @@
         <v>1</v>
       </c>
       <c r="DI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK9" t="n">
         <v>1</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP9" t="n">
         <v>1</v>
@@ -6161,13 +6161,13 @@
         <v>1</v>
       </c>
       <c r="DR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>1</v>
@@ -6176,13 +6176,13 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
@@ -6197,22 +6197,22 @@
         <v>1</v>
       </c>
       <c r="ED9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
         <v>1</v>
       </c>
       <c r="EI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
         <v>0</v>
@@ -6221,19 +6221,19 @@
         <v>1</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO9" t="n">
         <v>1</v>
       </c>
       <c r="EP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ9" t="n">
         <v>1</v>
@@ -6242,31 +6242,31 @@
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FB9" t="n">
         <v>0</v>
@@ -6278,193 +6278,193 @@
         <v>1</v>
       </c>
       <c r="FE9" t="n">
-        <v>2.889221556886227</v>
+        <v>2.103293413173652</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.538922155688622</v>
+        <v>5.845808383233534</v>
       </c>
       <c r="FG9" t="n">
-        <v>43.75748502994012</v>
+        <v>43.8435628742515</v>
       </c>
       <c r="FH9" t="n">
-        <v>12.18562874251497</v>
+        <v>12.27619760479042</v>
       </c>
       <c r="FI9" t="n">
-        <v>150.1047904191617</v>
+        <v>130.3615269461078</v>
       </c>
       <c r="FJ9" t="n">
-        <v>34.34131736526946</v>
+        <v>40.92065868263474</v>
       </c>
       <c r="FK9" t="n">
-        <v>18.27844311377245</v>
+        <v>11.10703592814371</v>
       </c>
       <c r="FL9" t="n">
-        <v>59.26646706586826</v>
+        <v>54.36601796407187</v>
       </c>
       <c r="FM9" t="n">
-        <v>1782.979041916167</v>
+        <v>1583.044910179641</v>
       </c>
       <c r="FN9" t="n">
-        <v>42.64970059880239</v>
+        <v>38.58233532934132</v>
       </c>
       <c r="FO9" t="n">
-        <v>29.91017964071856</v>
+        <v>30.98278443113773</v>
       </c>
       <c r="FP9" t="n">
-        <v>31.57185628742515</v>
+        <v>29.81362275449102</v>
       </c>
       <c r="FQ9" t="n">
-        <v>62.03592814371257</v>
+        <v>58.45808383233533</v>
       </c>
       <c r="FR9" t="n">
-        <v>4.985029940119761</v>
+        <v>7.01497005988024</v>
       </c>
       <c r="FS9" t="n">
-        <v>17.17065868263473</v>
+        <v>16.36826347305389</v>
       </c>
       <c r="FT9" t="n">
-        <v>42.09580838323352</v>
+        <v>49.68937125748504</v>
       </c>
       <c r="FU9" t="n">
-        <v>152.874251497006</v>
+        <v>151.4064371257485</v>
       </c>
       <c r="FV9" t="n">
-        <v>1463.383233532934</v>
+        <v>1274.970808383234</v>
       </c>
       <c r="FW9" t="n">
-        <v>1217.455089820359</v>
+        <v>1037.046407185629</v>
       </c>
       <c r="FX9" t="n">
-        <v>230.2529940119761</v>
+        <v>237.8659431137725</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.4727183563906669</v>
+        <v>0.317490824802009</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.7934877371693395</v>
+        <v>0.7536846592175451</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.2042127865481159</v>
+        <v>0.4690565297975478</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.197302364967035</v>
+        <v>1.312059214903526</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.1114955439840365</v>
+        <v>0.119815116794772</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.2904109105857351</v>
+        <v>0.3516875316322249</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.302529940119761</v>
+        <v>2.378659431137725</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.181049624479195</v>
+        <v>1.200733884934809</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.1603018719487479</v>
+        <v>0.1316707560639934</v>
       </c>
       <c r="GH9" t="n">
-        <v>1.497976462018654</v>
+        <v>1.295594213990443</v>
       </c>
       <c r="GI9" t="n">
-        <v>1.483394261937432</v>
+        <v>1.319562142661732</v>
       </c>
       <c r="GJ9" t="n">
-        <v>0.1444472466135548</v>
+        <v>0.144141628963349</v>
       </c>
       <c r="GK9" t="n">
-        <v>0.4610778443113777</v>
+        <v>-1.019461077844312</v>
       </c>
       <c r="GL9" t="n">
-        <v>-12.55748502994012</v>
+        <v>-9.455838323353298</v>
       </c>
       <c r="GM9" t="n">
-        <v>-0.5856287425149702</v>
+        <v>0.9962574850299379</v>
       </c>
       <c r="GN9" t="n">
-        <v>-4.904790419161685</v>
+        <v>6.586077844311347</v>
       </c>
       <c r="GO9" t="n">
-        <v>-17.94131736526946</v>
+        <v>0.1032934131736454</v>
       </c>
       <c r="GP9" t="n">
-        <v>-4.278443113772454</v>
+        <v>-0.851047904191617</v>
       </c>
       <c r="GQ9" t="n">
-        <v>-27.26646706586826</v>
+        <v>16.82260479041916</v>
       </c>
       <c r="GR9" t="n">
-        <v>57.82095808383247</v>
+        <v>86.87125748502967</v>
       </c>
       <c r="GS9" t="n">
-        <v>-11.04970059880239</v>
+        <v>8.474550898203589</v>
       </c>
       <c r="GT9" t="n">
-        <v>-15.91017964071856</v>
+        <v>-5.644461077844316</v>
       </c>
       <c r="GU9" t="n">
-        <v>-19.17185628742515</v>
+        <v>8.797155688622752</v>
       </c>
       <c r="GV9" t="n">
-        <v>-42.43592814371257</v>
+        <v>13.33383233532933</v>
       </c>
       <c r="GW9" t="n">
-        <v>-3.78502994011976</v>
+        <v>-3.998502994011977</v>
       </c>
       <c r="GX9" t="n">
-        <v>-8.77065868263473</v>
+        <v>4.74700598802395</v>
       </c>
       <c r="GY9" t="n">
-        <v>-14.49580838323352</v>
+        <v>11.24326347305388</v>
       </c>
       <c r="GZ9" t="n">
-        <v>-56.47425149700598</v>
+        <v>48.28368263473052</v>
       </c>
       <c r="HA9" t="n">
-        <v>174.6167664670661</v>
+        <v>92.09206586826326</v>
       </c>
       <c r="HB9" t="n">
-        <v>280.1449101796406</v>
+        <v>48.88173652694604</v>
       </c>
       <c r="HC9" t="n">
-        <v>-47.53299401197609</v>
+        <v>-1.797230538922207</v>
       </c>
       <c r="HD9" t="n">
-        <v>0.02546346179115128</v>
+        <v>0.1601164606271327</v>
       </c>
       <c r="HE9" t="n">
-        <v>0.06469408101247864</v>
+        <v>0.4043035310685491</v>
       </c>
       <c r="HF9" t="n">
-        <v>-0.01031779265312199</v>
+        <v>0.2741766467065868</v>
       </c>
       <c r="HG9" t="n">
-        <v>-0.7513927190573895</v>
+        <v>0.1062880191996958</v>
       </c>
       <c r="HH9" t="n">
-        <v>-0.07265084174708507</v>
+        <v>0.03834304486177842</v>
       </c>
       <c r="HI9" t="n">
-        <v>-0.1708185752464397</v>
+        <v>0.1151660514088267</v>
       </c>
       <c r="HJ9" t="n">
-        <v>-0.4753299401197606</v>
+        <v>-0.01797230538922268</v>
       </c>
       <c r="HK9" t="n">
-        <v>-0.2089861324157033</v>
+        <v>0.3031487872293812</v>
       </c>
       <c r="HL9" t="n">
-        <v>-0.001303430070839412</v>
+        <v>0.007522862562267391</v>
       </c>
       <c r="HM9" t="n">
-        <v>-0.04246608272568531</v>
+        <v>0.07725133426998632</v>
       </c>
       <c r="HN9" t="n">
-        <v>-0.107958045785546</v>
+        <v>0.07372029198906205</v>
       </c>
       <c r="HO9" t="n">
-        <v>-0.08905079563058638</v>
+        <v>0.03706865948678184</v>
       </c>
     </row>
     <row r="10">
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -6490,31 +6490,31 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -6526,19 +6526,19 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -6547,25 +6547,25 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -6586,13 +6586,13 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -6601,10 +6601,10 @@
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
         <v>0</v>
@@ -6613,10 +6613,10 @@
         <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -6625,34 +6625,34 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH10" t="n">
         <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -6661,130 +6661,130 @@
         <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.537425149700599</v>
+        <v>3.233532934131737</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.145508982035928</v>
+        <v>6.359880239520957</v>
       </c>
       <c r="BO10" t="n">
-        <v>26.2125748502994</v>
+        <v>32.77784431137724</v>
       </c>
       <c r="BP10" t="n">
-        <v>10.48502994011976</v>
+        <v>12.23053892215569</v>
       </c>
       <c r="BQ10" t="n">
-        <v>120.5778443113772</v>
+        <v>150.1910179640718</v>
       </c>
       <c r="BR10" t="n">
-        <v>22.54281437125749</v>
+        <v>27.88562874251497</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.388023952095809</v>
+        <v>17.61197604790419</v>
       </c>
       <c r="BT10" t="n">
-        <v>28.83383233532934</v>
+        <v>42.56227544910179</v>
       </c>
       <c r="BU10" t="n">
-        <v>1517.183832335329</v>
+        <v>1770.003592814371</v>
       </c>
       <c r="BV10" t="n">
-        <v>34.60059880239521</v>
+        <v>32.28862275449102</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.25179640718563</v>
+        <v>12.71976047904191</v>
       </c>
       <c r="BX10" t="n">
-        <v>21.49431137724551</v>
+        <v>28.37485029940119</v>
       </c>
       <c r="BY10" t="n">
-        <v>66.05568862275449</v>
+        <v>39.62694610778443</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.24251497005988</v>
+        <v>2.935329341317365</v>
       </c>
       <c r="CA10" t="n">
-        <v>23.59131736526946</v>
+        <v>15.65508982035928</v>
       </c>
       <c r="CB10" t="n">
-        <v>41.94011976047904</v>
+        <v>38.64850299401197</v>
       </c>
       <c r="CC10" t="n">
-        <v>150.9844311377246</v>
+        <v>114.4778443113772</v>
       </c>
       <c r="CD10" t="n">
-        <v>1261.873353293413</v>
+        <v>1557.192215568862</v>
       </c>
       <c r="CE10" t="n">
-        <v>1057.415269461078</v>
+        <v>1376.669461077844</v>
       </c>
       <c r="CF10" t="n">
-        <v>216.7255688622754</v>
+        <v>213.0559880239521</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.2999883566200931</v>
+        <v>0.5420264233437886</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.9786027944111777</v>
+        <v>1.06813373253493</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.2875440029032844</v>
+        <v>0.2989687292082501</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.081750978562356</v>
+        <v>0.8697272122421821</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0556838135160768</v>
+        <v>0.06699181483357963</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.3311247804421812</v>
+        <v>0.2109314744312841</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.167255688622755</v>
+        <v>2.13055988023952</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.391704192828917</v>
+        <v>1.413795293000999</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.09822515841761087</v>
+        <v>0.1224868728792389</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.20644876753233</v>
+        <v>1.499745351721846</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1.225573693630063</v>
+        <v>1.45431129361876</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.07226970767039818</v>
+        <v>0.09396024134042685</v>
       </c>
       <c r="CS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC10" t="n">
         <v>1</v>
@@ -6796,13 +6796,13 @@
         <v>1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -6811,13 +6811,13 @@
         <v>1</v>
       </c>
       <c r="DK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN10" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
         <v>1</v>
@@ -6841,10 +6841,10 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
@@ -6859,13 +6859,13 @@
         <v>1</v>
       </c>
       <c r="EA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>1</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH10" t="n">
         <v>1</v>
@@ -6886,256 +6886,256 @@
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK10" t="n">
         <v>1</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM10" t="n">
         <v>1</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO10" t="n">
         <v>1</v>
       </c>
       <c r="EP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER10" t="n">
         <v>1</v>
       </c>
       <c r="ES10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV10" t="n">
         <v>1</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
         <v>0</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD10" t="n">
         <v>1</v>
       </c>
       <c r="FE10" t="n">
-        <v>3.368263473053892</v>
+        <v>5</v>
       </c>
       <c r="FF10" t="n">
-        <v>3.657185628742515</v>
+        <v>6.052395209580839</v>
       </c>
       <c r="FG10" t="n">
-        <v>37.09431137724551</v>
+        <v>38.64221556886228</v>
       </c>
       <c r="FH10" t="n">
-        <v>12.01646706586826</v>
+        <v>13.03592814371257</v>
       </c>
       <c r="FI10" t="n">
-        <v>135.8383233532934</v>
+        <v>168.5359281437126</v>
       </c>
       <c r="FJ10" t="n">
-        <v>40.22904191616767</v>
+        <v>18.62275449101796</v>
       </c>
       <c r="FK10" t="n">
-        <v>17.76347305389222</v>
+        <v>16.29491017964072</v>
       </c>
       <c r="FL10" t="n">
-        <v>53.81287425149701</v>
+        <v>37.71107784431138</v>
       </c>
       <c r="FM10" t="n">
-        <v>1545.944610778443</v>
+        <v>2184.914670658683</v>
       </c>
       <c r="FN10" t="n">
-        <v>39.18413173652695</v>
+        <v>33.05538922155689</v>
       </c>
       <c r="FO10" t="n">
-        <v>15.67365269461078</v>
+        <v>13.96706586826347</v>
       </c>
       <c r="FP10" t="n">
-        <v>21.42065868263473</v>
+        <v>13.03592814371257</v>
       </c>
       <c r="FQ10" t="n">
-        <v>61.12724550898204</v>
+        <v>22.81287425149701</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.657185628742515</v>
+        <v>1.396706586826347</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.15119760479042</v>
+        <v>12.10479041916168</v>
       </c>
       <c r="FT10" t="n">
-        <v>37.61676646706587</v>
+        <v>36.77994011976048</v>
       </c>
       <c r="FU10" t="n">
-        <v>129.0464071856287</v>
+        <v>115.4610778443114</v>
       </c>
       <c r="FV10" t="n">
-        <v>1281.059880239521</v>
+        <v>1954.458083832335</v>
       </c>
       <c r="FW10" t="n">
-        <v>1077.302395209581</v>
+        <v>1785.922155688623</v>
       </c>
       <c r="FX10" t="n">
-        <v>218.072754491018</v>
+        <v>212.485628742515</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.2493332681955437</v>
+        <v>0.4394351988663366</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.9196955157284499</v>
+        <v>0.8362772290916004</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0949918345127926</v>
+        <v>0.1739488056853326</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.7781211469834225</v>
+        <v>0.439057948039984</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1112540505065995</v>
+        <v>0.04519827842479827</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.2718095515829536</v>
+        <v>0.1404491518656477</v>
       </c>
       <c r="GE10" t="n">
-        <v>2.180727544910179</v>
+        <v>2.12485628742515</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.381106770416387</v>
+        <v>1.051594430187244</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1200335132130391</v>
+        <v>0.1622254977030856</v>
       </c>
       <c r="GH10" t="n">
-        <v>1.359778892902655</v>
+        <v>1.691841455471072</v>
       </c>
       <c r="GI10" t="n">
-        <v>1.34997946838972</v>
+        <v>1.601892793565749</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.1485921437708725</v>
+        <v>0.06412560023239978</v>
       </c>
       <c r="GK10" t="n">
-        <v>-0.511676646706587</v>
+        <v>0.3074850299401186</v>
       </c>
       <c r="GL10" t="n">
-        <v>-10.88173652694611</v>
+        <v>-5.864371257485033</v>
       </c>
       <c r="GM10" t="n">
-        <v>-1.531437125748502</v>
+        <v>-0.8053892215568865</v>
       </c>
       <c r="GN10" t="n">
-        <v>-15.26047904191617</v>
+        <v>-18.34491017964075</v>
       </c>
       <c r="GO10" t="n">
-        <v>-17.68622754491018</v>
+        <v>9.262874251497003</v>
       </c>
       <c r="GP10" t="n">
-        <v>-9.375449101796407</v>
+        <v>1.317065868263469</v>
       </c>
       <c r="GQ10" t="n">
-        <v>-24.97904191616767</v>
+        <v>4.851197604790414</v>
       </c>
       <c r="GR10" t="n">
-        <v>-28.76077844311385</v>
+        <v>-414.9110778443114</v>
       </c>
       <c r="GS10" t="n">
-        <v>-4.583532934131739</v>
+        <v>-0.7667664670658709</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.5781437125748496</v>
+        <v>-1.247305389221559</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.07365269461077872</v>
+        <v>15.33892215568862</v>
       </c>
       <c r="GV10" t="n">
-        <v>4.928443113772452</v>
+        <v>16.81407185628742</v>
       </c>
       <c r="GW10" t="n">
-        <v>1.585329341317365</v>
+        <v>1.538622754491018</v>
       </c>
       <c r="GX10" t="n">
-        <v>8.440119760479041</v>
+        <v>3.550299401197602</v>
       </c>
       <c r="GY10" t="n">
-        <v>4.32335329341317</v>
+        <v>1.868562874251488</v>
       </c>
       <c r="GZ10" t="n">
-        <v>21.93802395209582</v>
+        <v>-0.9832335329341646</v>
       </c>
       <c r="HA10" t="n">
-        <v>-19.18652694610773</v>
+        <v>-397.2658682634733</v>
       </c>
       <c r="HB10" t="n">
-        <v>-19.88712574850319</v>
+        <v>-409.2526946107789</v>
       </c>
       <c r="HC10" t="n">
-        <v>-1.347185628742551</v>
+        <v>0.5703592814370779</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.05065508842454944</v>
+        <v>0.102591224477452</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.05890727868272783</v>
+        <v>0.2318565034433296</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.1925521683904918</v>
+        <v>0.1250199235229175</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3036298315789333</v>
+        <v>0.4306692642021981</v>
       </c>
       <c r="HH10" t="n">
-        <v>-0.05557023699052265</v>
+        <v>0.02179353640878136</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.05931522885922769</v>
+        <v>0.07048232256563641</v>
       </c>
       <c r="HJ10" t="n">
-        <v>-0.01347185628742453</v>
+        <v>0.005703592814370495</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.01059742241253048</v>
+        <v>0.3622008628137547</v>
       </c>
       <c r="HL10" t="n">
-        <v>-0.02180835479542823</v>
+        <v>-0.03973862482384663</v>
       </c>
       <c r="HM10" t="n">
-        <v>-0.1533301253703252</v>
+        <v>-0.1920961037492259</v>
       </c>
       <c r="HN10" t="n">
-        <v>-0.1244057747596572</v>
+        <v>-0.1475814999469889</v>
       </c>
       <c r="HO10" t="n">
-        <v>-0.0763224361004743</v>
+        <v>0.02983464110802707</v>
       </c>
     </row>
   </sheetData>
